--- a/reference/governadores.xlsx
+++ b/reference/governadores.xlsx
@@ -784,12 +784,12 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Renato Casagrande </t>
+          <t>Ricardo Ferraço</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> PSB </t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Ricardo Ferraço </t>
+          <t>Camillo Neves</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">

--- a/reference/governadores.xlsx
+++ b/reference/governadores.xlsx
@@ -1183,12 +1183,12 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Cláudio Castro </t>
+          <t>Ricardo Couto (desembargador, governador interino)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> PL </t>
+          <t>— (magistrado, sem partido)</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1198,17 +1198,13 @@
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Thiago Pampolha </t>
+          <t>(vago desde mai/2025)</t>
         </is>
       </c>
       <c r="F20" s="3" t="n">
         <v>2022</v>
       </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/claudiocastrorj/</t>
-        </is>
-      </c>
+      <c r="G20" s="5" t="n"/>
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
